--- a/tests/fixtures/import/real-shaped/jp-gift-history-287.xlsx
+++ b/tests/fixtures/import/real-shaped/jp-gift-history-287.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +48,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,7 +448,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>45293</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -471,7 +471,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>45294</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>45296</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>45302</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>For Alridge Ashville Family</t>
+          <t>For Jody Ashville Family</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>45306</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>45316</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Alshaw Linwood Everlow the Warbrook</t>
+          <t>Cash for Taco the Sheep</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>45321</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>45334</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Morworth</t>
+          <t>Paypal</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024 Bourbon &amp; Breeders Ball: 1/2 Bronze Sponsor (Langley Stonegate Harwen Dunley)</t>
+          <t>2024 Bourbon &amp; Breeders Ball: 1/2 Bronze Sponsor (splitting with Harwen Dunley)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024 Bourbon &amp; Breeders Ball: 1/2 Bronze Sponsor (Ringland Stonegate Mara Foxfield)</t>
+          <t>2024 Bourbon &amp; Breeders Ball: 1/2 Bronze Sponsor (split with Mara Foxfield)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024 Bourbon &amp; Breeders Ball: Roswood Sponsor</t>
+          <t>2024 Bourbon &amp; Breeders Ball: Logo Sponsor</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024 Bourbon &amp; Breeders Ball: Bronze Pemwell</t>
+          <t>2024 Bourbon &amp; Breeders Ball: Bronze Sposorship</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45377</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45380</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Alshaw Fairwell Stanland Everhurst J &amp; H Lindale</t>
+          <t>Cash Fairwell received Everhurst J &amp; H Booth</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45390</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Marbury Woodgate Warworth</t>
+          <t>Boehringer Ingleheim Employee</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2024 Bourbon &amp; Breeders Ball Glengate: Silver</t>
+          <t>2024 Bourbon &amp; Breeders Ball Sponsorship: Silver</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2024 Bourbon &amp; Breeders Ball: Gold Glengate</t>
+          <t>2024 Bourbon &amp; Breeders Ball: Gold Sponsorship</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Morworth (Goldwell of Belric Northgate Fairmore)</t>
+          <t>PayPal (Friend of Belric Kelby's Parents)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45426</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cardlow Sponsor Linwood the 2024 Bourbon &amp; Warfield Ball</t>
+          <t>Platinum Sponsor for the 2024 Bourbon &amp; Breeder's Ball</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45428</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Bourbon &amp; Breeders Ball: 2024 Cardlow Glengate</t>
+          <t>Bourbon &amp; Breeders Ball: 2024 Platinum Sponsorship</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45428</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Bourbon &amp; Breeders Ball: 2024 Roswood Sponsor</t>
+          <t>Bourbon &amp; Breeders Ball: 2024 Logo Sponsor</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45440</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Morworth (Goldwell of Wilana Cardridge)</t>
+          <t>PayPal (Friend of Wilana Cardridge)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45455</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45476</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2024 Bourbon &amp; Breeders Ball - Cardlow Glengate</t>
+          <t>2024 Bourbon &amp; Breeders Ball - Platinum Sponsorship</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45482</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45482</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45484</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Whitville Glengate</t>
+          <t>Supplies Sponsorship</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Bourbon &amp; Breeders Ball: 2024 Roswood Sponsor</t>
+          <t>Bourbon &amp; Breeders Ball: 2024 Logo Sponsor</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Refund of Sales Tax Thornmore Cranwell Salwick Warby Ringlow</t>
+          <t>Refund of Sales Tax that was charged by accident</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>On Ringham Ivoina Blackshaw</t>
+          <t>On Behalf Ivoina Crouse</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Pemville From Kelridge Whitworth Auction</t>
+          <t>Credit From We Do Auction</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Bourbon &amp; Stonebrook Gala:Roswood Sponsor (Glencombe Hartridge Langland)</t>
+          <t>Bourbon &amp; Breeder Gala:Logo Sponsor (Includes Two Tickets)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Selin and Orlie Kelworth In Memory of Loris Gilo</t>
+          <t>Selin and Orlie Marshaw-Donation- In Memory of Loris Gilo</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Bourbon &amp; Breeders Ball: Silver Glengate</t>
+          <t>Bourbon &amp; Breeders Ball: Silver Sponsorship</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Bourbon &amp; Breeders Ball: Gold Glengate</t>
+          <t>Bourbon &amp; Breeders Ball: Gold Sponsorship</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Bourbon &amp; Breeders Ball: Roswood Sponsor (Glencombe 2 Langland)</t>
+          <t>Bourbon &amp; Breeders Ball: Logo Sponsor (Includes 2 Tickets)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45523</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45525</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45527</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2024 Bourbon Ball Event: Sponsor Roswood - Verric Stanwell Alworth</t>
+          <t>2024 Bourbon Ball Event: Sponsor Logo - Verric Stanwell Alworth</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2024 Ashstead &amp; Breeders Kinlow Roswood Sponsor</t>
+          <t>2024 Bourbone &amp; Breeders Gala- Logo Sponsor</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45546</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2024 Bourbon &amp; Breeders Ball - Foxhurst Linwood Dunland</t>
+          <t>2024 Bourbon &amp; Breeders Ball - Table for Ten</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45551</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Donation In Memory of Loris Gilo Warby Cardbury Cardby</t>
+          <t>Donation In Memory of Loris Gilo by Cardbury Cardby</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45551</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45551</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45551</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45551</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45551</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45551</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45551</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45551</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45552</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Donation - Joy Oakmere Linwood Loris Gilo</t>
+          <t>Donation - Joy Oakmere for Loris Gilo</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45558</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Marmore Northham -Salwood</t>
+          <t>Marmore Northham -donation</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45558</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45558</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45559</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Donation: Perel Warville (In Stanhurst of Loris Gilo)</t>
+          <t>Donation: Perel Warville (In memory of Loris Gilo)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2024 Bourbon &amp; Breeders Gala Silver Glengate</t>
+          <t>2024 Bourbon &amp; Breeders Gala Silver Sponsorship</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45572</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2024 Bourbon &amp; Breeders Roswood Glengate - Lane Salworth Glenbrook LLC</t>
+          <t>2024 Bourbon &amp; Breeders Logo Sponsorship - Lane Salworth Glenbrook LLC</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45579</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2024 Bourbon and Breeders Ball - Roswood Glengate - Caldfield Lexington, LLC</t>
+          <t>2024 Bourbon and Breeders Ball - Logo Sponsorship - Caldfield Lexington, LLC</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2024 Bourbon &amp; Breeders Ball: Roswood Sponsor</t>
+          <t>2024 Bourbon &amp; Breeders Ball: Logo Sponsor</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Caldford Woodham Rosbrook Stonefield Stonegate MARCOMBE Stonewood Salley Ashby Oakstead</t>
+          <t>Prive Med Spa Facial with LED Red Light Therapy Mask</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>UK Stanton Dalmere Warby Mardale Ashworth Goldhurst</t>
+          <t>UK Basketball signed by Coach Popes Team</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wine Rosby Stonegate Caldham</t>
+          <t>Wine Cart with Accessories</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Versailles Warby Foxstead Linwood 4 Stonegate Oakwell Stoneridge Rosgate Linland</t>
+          <t>Versailles by Rail for 4 with a Ricardos gift card</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Golddale Langton Northbrook Dalham</t>
+          <t>Tobacco Stick Serving Tray</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Bradland Foxton 1 Redwell Pemwick, Stanmore Linwood 2 + Dinner Linwood 2 Everhurst 33 Stoneford</t>
+          <t>Origin Hotel 1 night stay, Breakfast for 2 + Dinner for 2 Everhurst 33 Staves</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Kentucky Kinbrook &amp; Oakwell Rosgate Linland Stonestead Harthurst Branley</t>
+          <t>Kentucky Pillow &amp; a Gift Card from Front Porch</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Blackwick Stoneham Foxley</t>
+          <t>Brewster's Christmas Basket</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Dunwick FOXLOW Fitness &amp; Elstead</t>
+          <t>Cycle YOU Fitness &amp; Sauna</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Stoneland Caldmere Reddale and Warwell Glenlow Glenlow</t>
+          <t>Vera Caldmere tote and Plush Blanket Blanket</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>THORNSTEAD Halstead and Foxmere &amp; Dinner Everhurst Kinwell</t>
+          <t>IPM Pst and Termite &amp; Dinner Everhurst Valora's</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -2315,12 +2315,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1 Branwell Unlimited Ashgate Everhurst Redford Fitness Everhurst Dalton Thornfield</t>
+          <t>1 Year Unlimited Classes Everhurst Core Fitness Everhurst Keene Trace</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Bradby Everstead Linley Stanby Linwood 10 -12 Alwell Ashcombe</t>
+          <t>Chicken Salad Chick Catering for 10 -12 people Certificate</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SD Kelland Blackworth</t>
+          <t>SD Botox Package</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Blackmore &amp; Northbury Elcombe Blackworth</t>
+          <t>Blackmore &amp; Wachs Orthodontics Package</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -2387,12 +2387,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Stoneworth Rosham Linwood 4</t>
+          <t>Golf Outing for 4</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Northland Northby Salbrook Blackworth</t>
+          <t>Luxe Lounge MedSpa Package</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Blackdale Stoneworth Ashcombe</t>
+          <t>Top Golf Certificate</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Morfield Blackworth</t>
+          <t>Keeneland Package</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Dunmere Foxville Ringford</t>
+          <t>Mercedes Foxville Ringford</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -2477,12 +2477,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Whithurst Kellow &amp; Westbury Kinton Stonegate Oakwell Roslow Thornbrook Hartworth</t>
+          <t>Willow Homes &amp; Design Consultation with a Custom Paint Palette</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Aerial Caldmore Blackworth Warby Calora Hartland</t>
+          <t>Aerial Photography Package by Calora Hartland</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -2513,12 +2513,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Holwood Pemwick Everhurst the Oakshaw &amp; Iso Hartdale Faircombe</t>
+          <t>Overnight Stay Everhurst the Manchester &amp; Iso Beckbe Bag</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Rosmere Stanshaw Thornbury Oakwell Box -Foxlow Cranfield the Ringby</t>
+          <t>Tempur-Pedic Bed in a Box -You pick the size</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -2549,12 +2549,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Pemham Salbury Kindale Foxley</t>
+          <t>Stoops Game Day Basket</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Brangate Dunville Blackworth</t>
+          <t>Yeti Tailgate Package</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Glenhurst Alwick Blackworth</t>
+          <t>Outdoor Recreational Package</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Stoneton Linstead Faircombe</t>
+          <t>Ladies Goodie Bag</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Dunford U Elville Blackworth</t>
+          <t>Optimize U Wellness Package</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Dunwick Branworth</t>
+          <t>Cycle Bar</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Woodton Dunstead Caldlow Westlow Warby Silon Stoneville</t>
+          <t>Professional Head Shot Session by Silon Brennan</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Warwick Stanville Caldmore Westlow</t>
+          <t>Brittanie Stanville Photography Session</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Albury Ball Everford</t>
+          <t>Pickle Ball Set</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Foxley of Bourbon Cardwood Warby Stoneley &amp; Perel Dalhurst</t>
+          <t>Basket of Bourbon donated by Bevin &amp; Perel Dalhurst</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Roslow Holwick Goldford Thornhurst Cardwood Warby Falin &amp; Silo Saldale</t>
+          <t>Custom Painted Yard Jockey donated by Falin &amp; Silo Saldale</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2 UK Stanton Langland</t>
+          <t>2 UK Basketball Tickets</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Woodville &amp; J Warford</t>
+          <t>Maple &amp; J Bangle</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>IV Glenwood Northcombe Everhurst Solutions Morlow Northwick</t>
+          <t>IV Vitamin Infusion Everhurst Solutions Functional Medicine</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Hartstead Cardcombe Dunstead Northdale Foxhurst</t>
+          <t>Double Barrel Head End Table</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Linfield Ringford Marwell</t>
+          <t>Wilric's Ringford Wash</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Stanby Linwood 10 Stonegate Bradgate Linford</t>
+          <t>Catering for 10 with Hannah Linford</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>4 UK/Fairridge Stanton Langland</t>
+          <t>4 UK/Auburn Basketball Tickets</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -3034,12 +3034,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Dungate Care Carddale</t>
+          <t>Skin Care Fridge</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Glenby Thorndale Cardwell Rosgate Linland Linwood Oakwell Cardham</t>
+          <t>Mads Magical Moments Gift Card for a Balloon</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Caldhurst Holwick Ivoley Marley Redgate</t>
+          <t>Hand Painted Ivoley Marley Bottle</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Thornwell Ashdale 5 Alwood</t>
+          <t>Massage Envy 5 Pack</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Stanbrook Blackworth</t>
+          <t>Weller Package</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Woodstead Thorngate Rosgate Everford</t>
+          <t>Ethereal Brewing Gift Set</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Davett Glenmore Dunridge and Oakwell $300 Rosgate Linland Fairham Alby Woodmere</t>
+          <t>Davett Kors Purse and a $300 Gift Card to Bella Rose</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Alham Linlow Fairwick</t>
+          <t>Shelia Bayes Necklac</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -3178,12 +3178,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Langworth Fairford Ringgate</t>
+          <t>Anna Shae Jeweltry</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B132" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Halwood Kelbrook Northley Kelford</t>
+          <t>God's Finger Print Painting</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Dalwick Redham</t>
+          <t>Gentlemens Collection</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Caldley Northstead 4 UK Salmere Oakton Kentucky Langland Stonegate Kelbury Dunton</t>
+          <t>Lower Arena 4 UK vs Western Kentucky tickets with parking pass</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Woodbrook Kelgate Kinville Linwood 6 Stonestead Halley Wargate Linmere</t>
+          <t>Private Dinenr Party for 6 from La Bonne Vie</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>CJ Redville Rosgate Ashcombe</t>
+          <t>CJ Esthetics Gift Certificate</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Goldwick of the Thornley Rosgate Linland</t>
+          <t>Bite of the Bluegrass Gift Card</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B140" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Wine and Kelhurst Everhurst J Westbrook</t>
+          <t>Wine and Dine Everhurst J Cranville's</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="B141" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Anonymous Foxford - Morbrook Selo Redgate</t>
+          <t>Anonymous Foxford - Makers Selo Bottle</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45593</v>
       </c>
       <c r="B142" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="B143" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>U K Foxley Ball</t>
+          <t>U K Basket Ball</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45610</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Falric and Ulwen Warbury - Maron and Lenett Bradbrook - Thornham Cardwell Blackbrook</t>
+          <t>Falric and Ulwen Warbury - Maron and Lenett Bradbrook - Stable Moments Program</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45629</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="B146" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Branfield Donation</t>
+          <t>End-of-Year Donation</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="B147" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Salmore Salwood</t>
+          <t>One-time donation</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="B148" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Branfield Donation</t>
+          <t>End-of-Year Donation</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45636</v>
       </c>
       <c r="B149" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Toris and Evermere Brookworth Oakwick Langwell Langwick</t>
+          <t>Toris and Phillip Brookworth Good Giving Challenge</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45636</v>
       </c>
       <c r="B150" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Ivoina Dunwell - Fairhurst Donation</t>
+          <t>Ivoina Dunwell - Individual Donation</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45644</v>
       </c>
       <c r="B151" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025 Bourbon &amp; Breeders Ball: Roswood Glengate</t>
+          <t>2025 Bourbon &amp; Breeders Ball: Logo Sponsorship</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45646</v>
       </c>
       <c r="B152" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45653</v>
       </c>
       <c r="B153" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Salmore Rosgate (Ulwen Oakbury Marridge)</t>
+          <t>One-Time Gift (Ulwen Warbury's Mother)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45653</v>
       </c>
       <c r="B154" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Salmore Rosgate (Falric Oakbury Goldwell)</t>
+          <t>One-Time Gift (Falric Warbury's Friend)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45666</v>
       </c>
       <c r="B155" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Donation - Belley Glenridge</t>
+          <t>Donation - Belley Dian</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45666</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45666</v>
       </c>
       <c r="B157" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45666</v>
       </c>
       <c r="B158" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Alin and Dalbrook Ashham - Fairhurst Donation</t>
+          <t>Alin and Dalbrook Ashham - Individual Donation</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45677</v>
       </c>
       <c r="B159" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45677</v>
       </c>
       <c r="B160" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Salwood</t>
+          <t>donation</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45699</v>
       </c>
       <c r="B161" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Islie Kelby - Woodwell Westmere Donation</t>
+          <t>Islie Kelby - One Time Donation</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45699</v>
       </c>
       <c r="B162" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45699</v>
       </c>
       <c r="B163" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Dr. Rosa Woodmore -Woodwell Westmere Donation</t>
+          <t>Dr. Rosa Woodmore -one Time Donation</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45699</v>
       </c>
       <c r="B164" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Isa Marshaw -Woodwell Westmere Donation</t>
+          <t>Isa Marshaw -One Time Donation</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45699</v>
       </c>
       <c r="B165" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Gilley Everwick - Woodwell Westmere Donation</t>
+          <t>Gilley Everwick - One Time Donation</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45699</v>
       </c>
       <c r="B166" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45699</v>
       </c>
       <c r="B167" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Belton Salby Kelmere -Woodwell Westmere Donation</t>
+          <t>Belton Salby Kelmere -One Time Donation</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45699</v>
       </c>
       <c r="B168" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Brookham Kelshaw2025 Bourbon and Breeders Ball</t>
+          <t>Mordale-Rosa Thornshaw-2025 Bourbon and Breeders Ball</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45699</v>
       </c>
       <c r="B169" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Noria Gilo - Woodwell Westmere Donation</t>
+          <t>Noria Gilo - One Time Donation</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45750</v>
       </c>
       <c r="B170" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45750</v>
       </c>
       <c r="B171" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45761</v>
       </c>
       <c r="B172" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Morham Warham Langland - Selin Marshaw</t>
+          <t>Saturday Defender Tickets - Selin Marshaw</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45761</v>
       </c>
       <c r="B173" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Warham Westcombe Langland - Falia Stonemere</t>
+          <t>Defender Raffle Tickets - Falia Stonemere</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="B174" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Glenbury Warham Westcombe Langland</t>
+          <t>Friday Defender Raffle Tickets</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B175" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Islie Kelstead - Donation</t>
+          <t>Islie Barnet - Donation</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="B176" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Dalworth Blackby</t>
+          <t>Joseph Blackby</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45806</v>
       </c>
       <c r="B177" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Pemley Donation</t>
+          <t>Parent Donation</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45817</v>
       </c>
       <c r="B178" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B179" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Thornham Cardwell - Donation</t>
+          <t>Stable Moments - Donation</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45832</v>
       </c>
       <c r="B180" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Pemdale Cranwell Salwick 60 Marford Tax Warland Everville</t>
+          <t>Customer was Charged 60 cents Tax on Mugs</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45836</v>
       </c>
       <c r="B181" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025 Bourbon &amp; Warfield Ball: Cardlow Sponsor</t>
+          <t>2025 Bourbon &amp; Breeder's Ball: Platinum Sponsor</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="B182" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Race Donation #3770607: Ashridge Warley</t>
+          <t>Race Donation #3770607: Ashridge Odaie-Walter</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="B183" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="B184" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="B185" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45855</v>
       </c>
       <c r="B186" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>BLACKFIELD Langwell 360 Branham Belton and Blackton Foxwell - Donation</t>
+          <t>DAF giving 360 Branham Belton and Blackton Foxwell - Donation</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="B187" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="B188" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="B189" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45882</v>
       </c>
       <c r="B190" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Donation - Elton Westworth (Linshaw Ball)</t>
+          <t>Donation - Elton PieceQuilters (Martha Ball)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45882</v>
       </c>
       <c r="B191" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45882</v>
       </c>
       <c r="B192" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="B193" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025 Bourbon &amp; Warfield Ball:1/2 Silver Sponsor</t>
+          <t>2025 Bourbon &amp; Breeder's Ball:1/2 Silver Sponsor</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="B194" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="B195" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025 Bourbon &amp; Warfield Ball: Cardlow Sponsor</t>
+          <t>2025 Bourbon &amp; Breeder's Ball: Platinum Sponsor</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="B196" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025 Bourbon &amp; Warfield Ball: Roswood Sponsor</t>
+          <t>2025 Bourbon &amp; Breeder's Ball: Logo Sponsor</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="B197" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="B198" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="B199" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025 Bourbon &amp; Warfield Ball: Gold Sponsor</t>
+          <t>2025 Bourbon &amp; Breeder's Ball: Gold Sponsor</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="B200" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025 Bourbon &amp; Warfield Ball: Silver Sponsor</t>
+          <t>2025 Bourbon &amp; Breeder's Ball: Silver Sponsor</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="B201" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="B202" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025 Bourbon &amp; Warfield Ball: Roswood Sponsor</t>
+          <t>2025 Bourbon &amp; Breeder's Ball: Logo Sponsor</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="B203" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025 Bourbon &amp; Warfield Ball:Silver Sponsor</t>
+          <t>2025 Bourbon &amp; Breeder's Ball:Silver Sponsor</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="B204" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025 Bourbon &amp; Warfield Ball: Silver Sponsor</t>
+          <t>2025 Bourbon &amp; Breeder's Ball: Silver Sponsor</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45889</v>
       </c>
       <c r="B205" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45889</v>
       </c>
       <c r="B206" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45889</v>
       </c>
       <c r="B207" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="B208" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Donation - MARHURST Woodwick, LLC</t>
+          <t>Donation - MARHURST Reality, LLC</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45895</v>
       </c>
       <c r="B209" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Bourbon &amp; Stonebrook Gala: Roswood Sponsor</t>
+          <t>Bourbon &amp; Breeder Gala: Logo Sponsor</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="B210" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45924</v>
       </c>
       <c r="B211" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Bourbon &amp; Breeders Ball: Roswood Sponsor</t>
+          <t>Bourbon &amp; Breeders Ball: Logo Sponsor</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B212" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45938</v>
       </c>
       <c r="B213" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45945</v>
       </c>
       <c r="B214" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Belton and Fairville Foxwell - Donation</t>
+          <t>Belton and Dcik Foxwell - Donation</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45946</v>
       </c>
       <c r="B215" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Oakby Donation - Westgate Marlow Warmore Warridge</t>
+          <t>General Donation - Westgate Marlow Warmore Warridge</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45950</v>
       </c>
       <c r="B216" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025 Bourbon &amp; Breeders Ball:Roswood Glengate</t>
+          <t>2025 Bourbon &amp; Breeders Ball:Logo Sponsorship</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45952</v>
       </c>
       <c r="B217" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>J Thornland and C Thornland - Aldale Donation Blackgate</t>
+          <t>J Thornland and C Thornland - Memorial Donation Fanny</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="B218" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="B219" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="B220" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Wilric Thornland - Marwood of Joy</t>
+          <t>Wilric Thornland - Hour of Joy</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="B221" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Orlie Marshaw - Marwood of Joy, Donation</t>
+          <t>Orlie Marshaw - Hour of Joy, Donation</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="B222" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="B223" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Kelah Bradwood - Salton</t>
+          <t>Kelah Bradwood - Donate</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="B224" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="B225" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Isric Thornby -Marwood of Joy -Salwood</t>
+          <t>Isric Thornby -Hour of Joy -donation</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="B226" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="B227" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45970</v>
       </c>
       <c r="B228" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Halville Valon Lane - Oakby Donation</t>
+          <t>k Valon Lane - General Donation</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="B229" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B230" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Purchase of Oakwell Horse</t>
+          <t>Purchase of a Horse</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45995</v>
       </c>
       <c r="B231" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Oakby Donation - Valen Langhurst</t>
+          <t>General Donation - Valen Langhurst</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45996</v>
       </c>
       <c r="B232" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>46000</v>
       </c>
       <c r="B233" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>46000</v>
       </c>
       <c r="B234" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>46001</v>
       </c>
       <c r="B235" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>46007</v>
       </c>
       <c r="B236" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>OAKVILLE REDLEY - Cardmere Donation</t>
+          <t>OAKVILLE FOUNDATION - Business Donation</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>46007</v>
       </c>
       <c r="B237" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>OAKVILLE REDLEY - Cardmere Donation</t>
+          <t>OAKVILLE FOUNDATION - Business Donation</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>46007</v>
       </c>
       <c r="B238" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>46007</v>
       </c>
       <c r="B239" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>46008</v>
       </c>
       <c r="B240" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Thornham Cardwell Donation - The Ashham Family Foundation</t>
+          <t>Stable Moments Donation - The Ashham Family Foundation</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46010</v>
       </c>
       <c r="B241" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Woodworth Warland Westmore the Horse From Cardford Jenin</t>
+          <t>Reimbursement on buying the Horse From Cardford Jenin</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46013</v>
       </c>
       <c r="B242" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46014</v>
       </c>
       <c r="B243" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46020</v>
       </c>
       <c r="B244" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46020</v>
       </c>
       <c r="B245" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46020</v>
       </c>
       <c r="B246" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46020</v>
       </c>
       <c r="B247" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46020</v>
       </c>
       <c r="B248" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46020</v>
       </c>
       <c r="B249" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="B250" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B251" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B252" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>46024</v>
       </c>
       <c r="B253" t="inlineStr">
@@ -5949,7 +5949,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>46030</v>
       </c>
       <c r="B254" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>46030</v>
       </c>
       <c r="B255" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="B256" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>46062</v>
       </c>
       <c r="B257" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Glenlow Linwood Elwick Perel - Donation</t>
+          <t>Blanket for Elwick Perel - Donation</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="B258" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Alshaw Donation - Belton Rosa Marmere</t>
+          <t>Cash Donation - Belton Rosa Marmere</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="B259" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Oakby Donation - Gara Salwell</t>
+          <t>General Donation - Gara Salwell</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>46085</v>
       </c>
       <c r="B260" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>46121</v>
       </c>
       <c r="B261" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Lane Salworth Glenbrook, LLC - Salwood</t>
+          <t>Lane Salworth Glenbrook, LLC - donation</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="B262" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Oakby Donation - Glendale Redmere</t>
+          <t>General Donation - Glendale Redmere</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B263" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Donation Thornbury of Verana Goldley</t>
+          <t>Donation in of Verana Goldley</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>46145</v>
       </c>
       <c r="B264" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Oakby Donation - Brookshaw Fairworth</t>
+          <t>General Donation - Brookshaw Fairworth</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="B265" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Orwen and Stanbury Northhurst - Donation</t>
+          <t>Orwen and Kathleen Northhurst - Donation</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="B266" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Oakby Donation - Nelric Marworth</t>
+          <t>General Donation - Nelric Marworth</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="B267" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Cardmere Donation - Hallow Elwood, LLC</t>
+          <t>Business Donation - Hallow Elwood, LLC</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="B268" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Fairhurst Donation - Morbury Kelley</t>
+          <t>Individual Donation - Morbury Kelley</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="B269" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Fairhurst Donation - Iston and Ulis Whitlow</t>
+          <t>Individual Donation - Iston and Ulis Whitlow</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B270" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Salwood Braddale Oakdale</t>
+          <t>donation Braddale Oakdale</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B271" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Stancombe - Whitmere and Morby Bradfield</t>
+          <t>onation - Rx and Morby Bradfield</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B272" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B273" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>46182</v>
       </c>
       <c r="B274" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Cardmere Contributions</t>
+          <t>Business Contributions</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>46183</v>
       </c>
       <c r="B275" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Oakby Donation - Selwen Standale</t>
+          <t>General Donation - Selwen Standale</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>46202</v>
       </c>
       <c r="B276" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>46216</v>
       </c>
       <c r="B277" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Bradhurst - Belton and Blackton Foxwell</t>
+          <t>Doantion - Belton and Blackton Foxwell</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>46221</v>
       </c>
       <c r="B278" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Goldlow Elworth - Woodwell Westmere Donation - Wilana Cardridge</t>
+          <t>Fence Repairs - One time Donation - Wilana Cardridge</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>46223</v>
       </c>
       <c r="B279" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Donation Linwood Auction Stonestead BRADLOW (Halmere Fairham Stonewood Westville)</t>
+          <t>Donation for Auction from BBB (Flights to Red Rock)</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="B280" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Oakby Donation: Brookshaw Fairworth</t>
+          <t>General Donation: Brookshaw Fairworth</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>46244</v>
       </c>
       <c r="B281" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Cardmere Donation</t>
+          <t>Business Donation</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>46246</v>
       </c>
       <c r="B282" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>46254</v>
       </c>
       <c r="B283" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>46266</v>
       </c>
       <c r="B284" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Oakby Donation - Brookshaw Fairworth</t>
+          <t>General Donation - Brookshaw Fairworth</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>46269</v>
       </c>
       <c r="B285" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>46282</v>
       </c>
       <c r="B286" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>46282</v>
       </c>
       <c r="B287" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B288" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Woodwell Westmere Donation: Kelwell Blackland Glenton Kelby</t>
+          <t>One Time Donation: Randal Blackland Glenton Kelby</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
